--- a/healthcare_forms/029_phq_9_rating_scale--healthcare_forms.xlsx
+++ b/healthcare_forms/029_phq_9_rating_scale--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1279,17 +1279,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>feel_good_choices</t>
+          <t>feel_good2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>better_than_usual</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Better than usual</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>better_than_usual</t>
+          <t>about_the_same_as_usual</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Better than usual</t>
+          <t>About the same as usual</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>about_the_same_as_usual</t>
+          <t>less_than_usual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>About the same as usual</t>
+          <t>Less than usual</t>
         </is>
       </c>
     </row>
@@ -1335,46 +1335,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>less_than_usual</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Less than usual</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>feel_good2_choices</t>
+          <t>have_you_had_a_trouble_sleeping_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>feel_good2_choices</t>
+          <t>have_you_had_a_trouble_sleeping_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Not at all</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>between_1-2_weeks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Between 1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1403,46 +1403,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>less_than_a_week</t>
+          <t>mostly_every_day</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Less than a week</t>
+          <t>Mostly every day</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>have_you_had_a_trouble_sleeping_choices</t>
+          <t>felt_too_full_of_energy_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>between_1-2_weeks</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Between 1-2 weeks</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>have_you_had_a_trouble_sleeping_choices</t>
+          <t>felt_too_full_of_energy_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mostly_every_day</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mostly every day</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>between_1-2_weeks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Between 1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1471,46 +1471,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>less_than_a_week</t>
+          <t>more_than_2_weeks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Less than a week</t>
+          <t>More than 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>felt_too_full_of_energy_choices</t>
+          <t>feel_tired_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>between_1-2_weeks</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Between 1-2 weeks</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>felt_too_full_of_energy_choices</t>
+          <t>feel_tired_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>more_than_2_weeks</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>More than 2 weeks</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>between_1-2_weeks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Between 1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1539,46 +1539,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>less_than_a_week</t>
+          <t>mostly_every_day</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Less than a week</t>
+          <t>Mostly every day</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>feel_tired_choices</t>
+          <t>feel_too_full_of_energy2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>between_1-2_weeks</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Between 1-2 weeks</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>feel_tired_choices</t>
+          <t>feel_too_full_of_energy2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mostly_every_day</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mostly every day</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>between_1-2_weeks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Between 1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1607,63 +1607,63 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>less_than_a_week</t>
+          <t>more_than_2_weeks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Less than a week</t>
+          <t>More than 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>feel_too_full_of_energy2_choices</t>
+          <t>difficulty_making_decision_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>between_1-2_weeks</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Between 1-2 weeks</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>feel_too_full_of_energy2_choices</t>
+          <t>difficulty_making_decision_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>more_than_2_weeks</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>More than 2 weeks</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>feel_too_full_of_energy2_choices</t>
+          <t>difficulty_making_decision_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>more_than_2_weeks</t>
+          <t>between_1-2_weeks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>More than 2 weeks</t>
+          <t>Between 1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -1675,53 +1675,53 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>mostly_every_day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mostly every day</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>difficulty_making_decision_choices</t>
+          <t>difficulty_concentrating_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>less_than_a_week</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Less than a week</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>difficulty_making_decision_choices</t>
+          <t>difficulty_concentrating_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>between_1-2_weeks</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Between 1-2 weeks</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>difficulty_making_decision_choices</t>
+          <t>difficulty_concentrating_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>difficulty_making_decision_choices</t>
+          <t>difficulty_concentrating_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>difficulty_concentrating_choices</t>
+          <t>enjoy_life_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>difficulty_concentrating_choices</t>
+          <t>enjoy_life_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>difficulty_concentrating_choices</t>
+          <t>enjoy_life_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,24 +1806,24 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>difficulty_concentrating_choices</t>
+          <t>enjoy_life_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>mostly_every_day</t>
+          <t>more_than_2_weeks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mostly every day</t>
+          <t>More than 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>enjoy_life_choices</t>
+          <t>feel_hopeful_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>enjoy_life_choices</t>
+          <t>feel_hopeful_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>enjoy_life_choices</t>
+          <t>feel_hopeful_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>enjoy_life_choices</t>
+          <t>feel_hopeful_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>feel_hopeful_choices</t>
+          <t>feel_happy_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>feel_hopeful_choices</t>
+          <t>feel_happy_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>feel_hopeful_choices</t>
+          <t>feel_happy_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>feel_hopeful_choices</t>
+          <t>feel_happy_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>feel_happy_choices</t>
+          <t>feel_guilty_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>feel_happy_choices</t>
+          <t>feel_guilty_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>feel_happy_choices</t>
+          <t>feel_guilty_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>feel_happy_choices</t>
+          <t>feel_guilty_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>feel_guilty_choices</t>
+          <t>feel_usefull_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>feel_guilty_choices</t>
+          <t>feel_usefull_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>feel_guilty_choices</t>
+          <t>feel_usefull_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>feel_guilty_choices</t>
+          <t>feel_usefull_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>feel_usefull_choices</t>
+          <t>feel_sad_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>feel_usefull_choices</t>
+          <t>feel_sad_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>feel_usefull_choices</t>
+          <t>feel_sad_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>feel_usefull_choices</t>
+          <t>feel_sad_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>feel_sad_choices</t>
+          <t>feel_angry_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>feel_sad_choices</t>
+          <t>feel_angry_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>feel_sad_choices</t>
+          <t>feel_angry_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>feel_sad_choices</t>
+          <t>feel_angry_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>feel_angry_choices</t>
+          <t>feel_nervous_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>feel_angry_choices</t>
+          <t>feel_nervous_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>feel_angry_choices</t>
+          <t>feel_nervous_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>feel_angry_choices</t>
+          <t>feel_nervous_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>feel_nervous_choices</t>
+          <t>have_trouble_with_sleep_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>feel_nervous_choices</t>
+          <t>have_trouble_with_sleep_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>feel_nervous_choices</t>
+          <t>have_trouble_with_sleep_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2350,7 +2350,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>feel_nervous_choices</t>
+          <t>have_trouble_with_sleep_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>have_trouble_with_sleep_choices</t>
+          <t>lost_temper_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>have_trouble_with_sleep_choices</t>
+          <t>lost_temper_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>have_trouble_with_sleep_choices</t>
+          <t>lost_temper_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2418,7 +2418,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>have_trouble_with_sleep_choices</t>
+          <t>lost_temper_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>lost_temper_choices</t>
+          <t>prefer_to_stay_at_home_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>lost_temper_choices</t>
+          <t>prefer_to_stay_at_home_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lost_temper_choices</t>
+          <t>prefer_to_stay_at_home_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2486,7 +2486,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>lost_temper_choices</t>
+          <t>prefer_to_stay_at_home_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2503,7 +2503,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>prefer_to_stay_at_home_choices</t>
+          <t>stay_in_touch_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2520,7 +2520,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>prefer_to_stay_at_home_choices</t>
+          <t>stay_in_touch_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2537,7 +2537,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>prefer_to_stay_at_home_choices</t>
+          <t>stay_in_touch_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>prefer_to_stay_at_home_choices</t>
+          <t>stay_in_touch_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>stay_in_touch_choices</t>
+          <t>enjoy_life2_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>stay_in_touch_choices</t>
+          <t>enjoy_life2_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>stay_in_touch_choices</t>
+          <t>enjoy_life2_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2622,7 +2622,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>stay_in_touch_choices</t>
+          <t>enjoy_life2_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>enjoy_life2_choices</t>
+          <t>feel_hopeful2_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>enjoy_life2_choices</t>
+          <t>feel_hopeful2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>enjoy_life2_choices</t>
+          <t>feel_hopeful2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>enjoy_life2_choices</t>
+          <t>feel_hopeful2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>feel_hopeful2_choices</t>
+          <t>feel_sad2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>feel_hopeful2_choices</t>
+          <t>feel_sad2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>feel_hopeful2_choices</t>
+          <t>feel_sad2_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>feel_hopeful2_choices</t>
+          <t>feel_sad2_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2767,74 +2767,6 @@
         </is>
       </c>
       <c r="C98" t="inlineStr">
-        <is>
-          <t>More than 2 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>feel_sad2_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>feel_sad2_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>less_than_a_week</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Less than a week</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>feel_sad2_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>between_1-2_weeks</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Between 1-2 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>feel_sad2_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>more_than_2_weeks</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
         <is>
           <t>More than 2 weeks</t>
         </is>
